--- a/progress.xlsx
+++ b/progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F11EF1-0DE4-412F-BA8D-9FD6EBF2334B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BE1854-80B5-4A14-BCDB-566D90C17F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="59">
   <si>
     <t>Task</t>
   </si>
@@ -663,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O108"/>
+  <dimension ref="A1:O142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -3658,6 +3658,560 @@
         <v>55</v>
       </c>
     </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>55</v>
+      </c>
+      <c r="B109" s="6">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>55</v>
+      </c>
+      <c r="B110" s="6">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2">
+        <v>46236</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>55</v>
+      </c>
+      <c r="B111" s="6">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>46237</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F111" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>55</v>
+      </c>
+      <c r="B112" s="6">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2">
+        <v>46238</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F112" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>55</v>
+      </c>
+      <c r="B113" s="6">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2">
+        <v>46239</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F113" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>55</v>
+      </c>
+      <c r="B114" s="6">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2">
+        <v>46240</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>55</v>
+      </c>
+      <c r="B115" s="6">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F115" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>55</v>
+      </c>
+      <c r="B116" s="6">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2">
+        <v>46242</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>55</v>
+      </c>
+      <c r="B117" s="6">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2">
+        <v>46243</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>55</v>
+      </c>
+      <c r="B118" s="6">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2">
+        <v>46244</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F118" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B119" s="6">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2">
+        <v>46245</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F119" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" s="6">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2">
+        <v>46246</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F120" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>55</v>
+      </c>
+      <c r="B121" s="6">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122" s="6">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2">
+        <v>46248</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>55</v>
+      </c>
+      <c r="B123" s="6">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2">
+        <v>46249</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F123" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>55</v>
+      </c>
+      <c r="B124" s="6">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2">
+        <v>46250</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>55</v>
+      </c>
+      <c r="B125" s="6">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2">
+        <v>46251</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F125" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>55</v>
+      </c>
+      <c r="B126" s="6">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2">
+        <v>46252</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>55</v>
+      </c>
+      <c r="B127" s="6">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2">
+        <v>46253</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>55</v>
+      </c>
+      <c r="B128" s="6">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2">
+        <v>46254</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>55</v>
+      </c>
+      <c r="B129" s="6">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2">
+        <v>46255</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>55</v>
+      </c>
+      <c r="B130" s="6">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2">
+        <v>46256</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>55</v>
+      </c>
+      <c r="B131" s="6">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2">
+        <v>46257</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F131" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>55</v>
+      </c>
+      <c r="B132" s="6">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2">
+        <v>46258</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>55</v>
+      </c>
+      <c r="B133" s="6">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2">
+        <v>46259</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" s="6">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2">
+        <v>46260</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F134" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>55</v>
+      </c>
+      <c r="B135" s="6">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2">
+        <v>46261</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>55</v>
+      </c>
+      <c r="B136" s="6">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2">
+        <v>46262</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>55</v>
+      </c>
+      <c r="B137" s="6">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2">
+        <v>46263</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>55</v>
+      </c>
+      <c r="B138" s="6">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2">
+        <v>46264</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" s="6">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2">
+        <v>46265</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F139" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>55</v>
+      </c>
+      <c r="B140" s="6">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2">
+        <v>46266</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B141" s="6"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B142" s="6"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BE1854-80B5-4A14-BCDB-566D90C17F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE0C072-482C-4FDE-A312-3FFAE143171F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="64">
   <si>
     <t>Task</t>
   </si>
@@ -262,6 +262,26 @@
   </si>
   <si>
     <t>Mob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asyraf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fremmy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ali</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong current. CTV unable to push on</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -315,7 +335,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,6 +345,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,7 +371,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -380,6 +406,16 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -663,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O142"/>
+  <dimension ref="A1:O152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4203,14 +4239,223 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B141" s="6"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="A141" t="s">
+        <v>55</v>
+      </c>
+      <c r="B141" s="6">
+        <v>0</v>
+      </c>
+      <c r="D141" s="2">
+        <v>46267</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B142" s="6"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="A142" t="s">
+        <v>55</v>
+      </c>
+      <c r="B142" s="6">
+        <v>0</v>
+      </c>
+      <c r="D142" s="2">
+        <v>46268</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>55</v>
+      </c>
+      <c r="B143" s="6">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2">
+        <v>46269</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F143" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="6">
+        <v>0</v>
+      </c>
+      <c r="D144" s="2">
+        <v>46270</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>55</v>
+      </c>
+      <c r="B145" s="6">
+        <v>0</v>
+      </c>
+      <c r="D145" s="2">
+        <v>46271</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F145" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>55</v>
+      </c>
+      <c r="B146" s="6">
+        <v>0</v>
+      </c>
+      <c r="D146" s="2">
+        <v>46272</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>55</v>
+      </c>
+      <c r="B147" s="6">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2">
+        <v>46273</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>55</v>
+      </c>
+      <c r="B148" s="6">
+        <v>0</v>
+      </c>
+      <c r="D148" s="2">
+        <v>46274</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F148" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>55</v>
+      </c>
+      <c r="B149" s="6">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2">
+        <v>46275</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F149" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>55</v>
+      </c>
+      <c r="B150" s="6">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2">
+        <v>46276</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F150" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>55</v>
+      </c>
+      <c r="B151" s="6">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2">
+        <v>46277</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F151" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B152" s="14">
+        <v>0</v>
+      </c>
+      <c r="C152" s="13">
+        <v>1</v>
+      </c>
+      <c r="D152" s="15">
+        <v>46278</v>
+      </c>
+      <c r="E152" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="H152" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J152" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K152" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE0C072-482C-4FDE-A312-3FFAE143171F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02627BB-9561-447C-90D3-D82C969E63AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4439,10 +4439,10 @@
         <v>46278</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G152" s="13" t="s">
         <v>60</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02627BB-9561-447C-90D3-D82C969E63AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E7A3F2-36C8-4B81-8E36-C937C152987F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="65">
   <si>
     <t>Task</t>
   </si>
@@ -277,12 +277,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Strong current. CTV unable to push on</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Ali</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Strong current. CTV unable to push on</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asyraf</t>
   </si>
 </sst>
 </file>
@@ -371,7 +373,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -417,6 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{82E2E59F-3CB1-4560-A332-AE3CB4876186}"/>
@@ -699,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O152"/>
+  <dimension ref="A1:O156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4451,11 +4454,93 @@
         <v>61</v>
       </c>
       <c r="J152" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K152" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="K152" s="13" t="s">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B153" s="6">
+        <v>0</v>
+      </c>
+      <c r="D153" s="17">
+        <v>46279</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G153" t="s">
+        <v>64</v>
+      </c>
+      <c r="J153" t="s">
         <v>63</v>
       </c>
+      <c r="K153" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B154" s="6">
+        <v>0</v>
+      </c>
+      <c r="D154" s="17">
+        <v>46280</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G154" t="s">
+        <v>64</v>
+      </c>
+      <c r="J154" t="s">
+        <v>63</v>
+      </c>
+      <c r="K154" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B155" s="6">
+        <v>0</v>
+      </c>
+      <c r="D155" s="17">
+        <v>46281</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G155" t="s">
+        <v>64</v>
+      </c>
+      <c r="J155" t="s">
+        <v>63</v>
+      </c>
+      <c r="K155" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A156" s="1"/>
+      <c r="B156" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E7A3F2-36C8-4B81-8E36-C937C152987F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496EAA5A-AB73-448A-AFB7-7D4FA9ED42E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="67">
   <si>
     <t>Task</t>
   </si>
@@ -285,6 +285,14 @@
   </si>
   <si>
     <t>Asyraf</t>
+  </si>
+  <si>
+    <t>Aiman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -373,7 +381,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -420,6 +428,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{82E2E59F-3CB1-4560-A332-AE3CB4876186}"/>
@@ -4505,11 +4524,17 @@
       <c r="G154" t="s">
         <v>64</v>
       </c>
+      <c r="H154" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I154" t="s">
+        <v>65</v>
+      </c>
       <c r="J154" t="s">
         <v>63</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
@@ -4531,16 +4556,53 @@
       <c r="G155" t="s">
         <v>64</v>
       </c>
+      <c r="H155" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I155" t="s">
+        <v>65</v>
+      </c>
       <c r="J155" t="s">
         <v>63</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>15</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="1"/>
-      <c r="B156" s="6"/>
+      <c r="A156" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B156" s="19">
+        <v>0</v>
+      </c>
+      <c r="C156" s="18">
+        <v>1</v>
+      </c>
+      <c r="D156" s="20">
+        <v>46282</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F156" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G156" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H156" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I156" t="s">
+        <v>65</v>
+      </c>
+      <c r="J156" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K156" s="18" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496EAA5A-AB73-448A-AFB7-7D4FA9ED42E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B94251-356D-413F-B7BD-D9D5FD8F6D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="69">
   <si>
     <t>Task</t>
   </si>
@@ -292,6 +292,14 @@
   </si>
   <si>
     <t>Training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong current. CTV turned back before entering the F2 wind farm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -381,7 +389,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -428,17 +436,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{82E2E59F-3CB1-4560-A332-AE3CB4876186}"/>
@@ -721,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O156"/>
+  <dimension ref="A1:O157"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4524,7 +4521,7 @@
       <c r="G154" t="s">
         <v>64</v>
       </c>
-      <c r="H154" s="18" t="s">
+      <c r="H154" t="s">
         <v>61</v>
       </c>
       <c r="I154" t="s">
@@ -4556,7 +4553,7 @@
       <c r="G155" t="s">
         <v>64</v>
       </c>
-      <c r="H155" s="18" t="s">
+      <c r="H155" t="s">
         <v>61</v>
       </c>
       <c r="I155" t="s">
@@ -4570,37 +4567,72 @@
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="18" t="s">
+      <c r="A156" t="s">
         <v>59</v>
       </c>
-      <c r="B156" s="19">
-        <v>0</v>
-      </c>
-      <c r="C156" s="18">
-        <v>1</v>
-      </c>
-      <c r="D156" s="20">
+      <c r="B156" s="6">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156" s="17">
         <v>46282</v>
       </c>
-      <c r="E156" s="21" t="s">
+      <c r="E156" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F156" s="22" t="s">
+      <c r="F156" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G156" s="18" t="s">
+      <c r="G156" t="s">
         <v>60</v>
       </c>
-      <c r="H156" s="18" t="s">
+      <c r="H156" t="s">
         <v>61</v>
       </c>
       <c r="I156" t="s">
         <v>65</v>
       </c>
-      <c r="J156" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="K156" s="18" t="s">
+      <c r="J156" t="s">
+        <v>8</v>
+      </c>
+      <c r="K156" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>67</v>
+      </c>
+      <c r="B157" s="6">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="D157" s="17">
+        <v>46283</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G157" t="s">
+        <v>60</v>
+      </c>
+      <c r="H157" t="s">
+        <v>61</v>
+      </c>
+      <c r="I157" t="s">
+        <v>10</v>
+      </c>
+      <c r="J157" t="s">
+        <v>8</v>
+      </c>
+      <c r="K157" t="s">
         <v>62</v>
       </c>
     </row>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B94251-356D-413F-B7BD-D9D5FD8F6D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6128A336-0D00-462C-BC10-B6852C39D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="74">
   <si>
     <t>Task</t>
   </si>
@@ -296,6 +296,27 @@
   </si>
   <si>
     <t>D05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong current. CTV turned back before entering the F2 wind farm.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>David</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Due to worsening weather, we came down from the tower at around 11:00.
+The Tetherline was damaged during AIB launch and was replaced with a spare.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong current. CTV unable to push on</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -389,7 +410,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,6 +457,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal 2" xfId="2" xr:uid="{82E2E59F-3CB1-4560-A332-AE3CB4876186}"/>
@@ -718,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:O163"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4636,6 +4660,207 @@
         <v>62</v>
       </c>
     </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B158" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="C158">
+        <v>3</v>
+      </c>
+      <c r="D158" s="17">
+        <v>46284</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G158" t="s">
+        <v>60</v>
+      </c>
+      <c r="H158" t="s">
+        <v>61</v>
+      </c>
+      <c r="I158" t="s">
+        <v>10</v>
+      </c>
+      <c r="J158" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="29" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B159" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+      <c r="D159" s="17">
+        <v>46285</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G159" t="s">
+        <v>60</v>
+      </c>
+      <c r="H159" t="s">
+        <v>61</v>
+      </c>
+      <c r="I159" t="s">
+        <v>10</v>
+      </c>
+      <c r="J159" t="s">
+        <v>70</v>
+      </c>
+      <c r="K159" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A160" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B160" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="D160" s="17">
+        <v>46286</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G160" t="s">
+        <v>60</v>
+      </c>
+      <c r="H160" t="s">
+        <v>61</v>
+      </c>
+      <c r="I160" t="s">
+        <v>10</v>
+      </c>
+      <c r="J160" t="s">
+        <v>70</v>
+      </c>
+      <c r="K160" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B161" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="C161">
+        <v>3</v>
+      </c>
+      <c r="D161" s="17">
+        <v>46287</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G161" t="s">
+        <v>60</v>
+      </c>
+      <c r="H161" t="s">
+        <v>61</v>
+      </c>
+      <c r="I161" t="s">
+        <v>10</v>
+      </c>
+      <c r="J161" t="s">
+        <v>8</v>
+      </c>
+      <c r="K161" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A162" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B162" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="D162" s="17">
+        <v>46288</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G162" t="s">
+        <v>60</v>
+      </c>
+      <c r="H162" t="s">
+        <v>61</v>
+      </c>
+      <c r="I162" t="s">
+        <v>10</v>
+      </c>
+      <c r="J162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B163" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="C163">
+        <v>3</v>
+      </c>
+      <c r="D163" s="17">
+        <v>46289</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G163" t="s">
+        <v>60</v>
+      </c>
+      <c r="H163" t="s">
+        <v>61</v>
+      </c>
+      <c r="I163" t="s">
+        <v>10</v>
+      </c>
+      <c r="J163" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6128A336-0D00-462C-BC10-B6852C39D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62142DCA-9E7F-4CAC-8237-AC31CA2787AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="76">
   <si>
     <t>Task</t>
   </si>
@@ -321,6 +321,14 @@
   </si>
   <si>
     <t>Strong current. CTV turned back before entering the F2 wind farm.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ali/Michael</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>David/Michael</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O163"/>
+  <dimension ref="A1:O166"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -754,7 +762,7 @@
     <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.09765625" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="137.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4801,9 +4809,7 @@
       <c r="A162" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B162" s="6">
-        <v>0.22</v>
-      </c>
+      <c r="B162" s="6"/>
       <c r="C162">
         <v>3</v>
       </c>
@@ -4833,9 +4839,7 @@
       <c r="A163" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B163" s="6">
-        <v>0.22</v>
-      </c>
+      <c r="B163" s="6"/>
       <c r="C163">
         <v>3</v>
       </c>
@@ -4859,6 +4863,93 @@
       </c>
       <c r="J163" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C164">
+        <v>3</v>
+      </c>
+      <c r="D164" s="17">
+        <v>46290</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G164" t="s">
+        <v>60</v>
+      </c>
+      <c r="H164" t="s">
+        <v>61</v>
+      </c>
+      <c r="I164" t="s">
+        <v>10</v>
+      </c>
+      <c r="J164" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A165" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C165">
+        <v>3</v>
+      </c>
+      <c r="D165" s="17">
+        <v>46291</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G165" t="s">
+        <v>60</v>
+      </c>
+      <c r="H165" t="s">
+        <v>61</v>
+      </c>
+      <c r="I165" t="s">
+        <v>10</v>
+      </c>
+      <c r="J165" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C166">
+        <v>3</v>
+      </c>
+      <c r="D166" s="17">
+        <v>46292</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G166" t="s">
+        <v>60</v>
+      </c>
+      <c r="H166" t="s">
+        <v>61</v>
+      </c>
+      <c r="I166" t="s">
+        <v>10</v>
+      </c>
+      <c r="J166" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62142DCA-9E7F-4CAC-8237-AC31CA2787AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFFF3D7-1A27-4F94-9229-EBFD1276BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4676,7 +4676,7 @@
         <v>0.1</v>
       </c>
       <c r="C158">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158" s="17">
         <v>46284</v>
@@ -4708,7 +4708,7 @@
         <v>0.22</v>
       </c>
       <c r="C159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D159" s="17">
         <v>46285</v>
@@ -4743,7 +4743,7 @@
         <v>0.22</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" s="17">
         <v>46286</v>
@@ -4778,7 +4778,7 @@
         <v>0.22</v>
       </c>
       <c r="C161">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D161" s="17">
         <v>46287</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B162" s="6"/>
       <c r="C162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D162" s="17">
         <v>46288</v>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="B163" s="6"/>
       <c r="C163">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D163" s="17">
         <v>46289</v>
@@ -4870,7 +4870,7 @@
         <v>69</v>
       </c>
       <c r="C164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164" s="17">
         <v>46290</v>
@@ -4899,7 +4899,7 @@
         <v>69</v>
       </c>
       <c r="C165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" s="17">
         <v>46291</v>
@@ -4928,7 +4928,7 @@
         <v>69</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" s="17">
         <v>46292</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFFF3D7-1A27-4F94-9229-EBFD1276BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727EED05-905A-4F60-9162-8290788D099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="77">
   <si>
     <t>Task</t>
   </si>
@@ -329,6 +329,10 @@
   </si>
   <si>
     <t>David/Michael</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power outage on the wind farm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4807,20 +4811,19 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B162" s="6"/>
-      <c r="C162">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B162" s="6">
+        <v>0</v>
       </c>
       <c r="D162" s="17">
         <v>46288</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G162" t="s">
         <v>60</v>
@@ -4833,6 +4836,9 @@
       </c>
       <c r="J162" t="s">
         <v>8</v>
+      </c>
+      <c r="K162" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727EED05-905A-4F60-9162-8290788D099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7D227-3F4B-4357-B477-1559B53EA634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4868,7 +4868,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC7D227-3F4B-4357-B477-1559B53EA634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67CD06D-04CD-4A09-8354-8DCA713D4822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4845,7 +4845,9 @@
       <c r="A163" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B163" s="6"/>
+      <c r="B163" s="6">
+        <v>0.22</v>
+      </c>
       <c r="C163">
         <v>1</v>
       </c>
@@ -4875,6 +4877,9 @@
       <c r="A164" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="B164" s="6">
+        <v>0.22</v>
+      </c>
       <c r="C164">
         <v>1</v>
       </c>
@@ -4904,6 +4909,9 @@
       <c r="A165" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="B165" s="6">
+        <v>0.22</v>
+      </c>
       <c r="C165">
         <v>1</v>
       </c>
@@ -4932,6 +4940,9 @@
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>69</v>
+      </c>
+      <c r="B166" s="6">
+        <v>0.22</v>
       </c>
       <c r="C166">
         <v>1</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67CD06D-04CD-4A09-8354-8DCA713D4822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C045C2F4-9E86-420A-BDE4-FD0C6E23E428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="78">
   <si>
     <t>Task</t>
   </si>
@@ -333,6 +333,10 @@
   </si>
   <si>
     <t>Power outage on the wind farm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Michael</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -758,15 +762,15 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.59765625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.59765625" customWidth="1"/>
-    <col min="6" max="6" width="15.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.09765625" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="137.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4870,7 +4874,7 @@
         <v>10</v>
       </c>
       <c r="J163" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C045C2F4-9E86-420A-BDE4-FD0C6E23E428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27858DE7-D6B7-48A1-814A-029B62133D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="78">
   <si>
     <t>Task</t>
   </si>
@@ -758,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O166"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4862,7 +4862,7 @@
         <v>41</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G163" t="s">
         <v>60</v>
@@ -4875,6 +4875,9 @@
       </c>
       <c r="J163" t="s">
         <v>77</v>
+      </c>
+      <c r="K163" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
@@ -4971,6 +4974,57 @@
       </c>
       <c r="J166" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D167" s="17">
+        <v>46293</v>
+      </c>
+      <c r="G167" t="s">
+        <v>60</v>
+      </c>
+      <c r="H167" t="s">
+        <v>61</v>
+      </c>
+      <c r="I167" t="s">
+        <v>10</v>
+      </c>
+      <c r="J167" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D168" s="17">
+        <v>46294</v>
+      </c>
+      <c r="G168" t="s">
+        <v>60</v>
+      </c>
+      <c r="H168" t="s">
+        <v>61</v>
+      </c>
+      <c r="I168" t="s">
+        <v>10</v>
+      </c>
+      <c r="J168" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D169" s="17">
+        <v>46295</v>
+      </c>
+      <c r="G169" t="s">
+        <v>60</v>
+      </c>
+      <c r="H169" t="s">
+        <v>61</v>
+      </c>
+      <c r="I169" t="s">
+        <v>10</v>
+      </c>
+      <c r="J169" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27858DE7-D6B7-48A1-814A-029B62133D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A113F6-AED9-47DB-B63F-A48530F2F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="78">
   <si>
     <t>Task</t>
   </si>
@@ -4862,7 +4862,7 @@
         <v>41</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G163" t="s">
         <v>60</v>
@@ -4875,9 +4875,6 @@
       </c>
       <c r="J163" t="s">
         <v>77</v>
-      </c>
-      <c r="K163" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A113F6-AED9-47DB-B63F-A48530F2F2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A35DCFB-58DD-4153-83FB-143434DCA358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="81">
   <si>
     <t>Task</t>
   </si>
@@ -337,6 +337,18 @@
   </si>
   <si>
     <t>Michael</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zaidi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fremmy/Zaidi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asyraf/Aiman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -767,8 +779,8 @@
     <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.59765625" customWidth="1"/>
     <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="137.8984375" bestFit="1" customWidth="1"/>
@@ -4649,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" s="17">
         <v>46283</v>
@@ -4832,12 +4844,6 @@
       <c r="G162" t="s">
         <v>60</v>
       </c>
-      <c r="H162" t="s">
-        <v>61</v>
-      </c>
-      <c r="I162" t="s">
-        <v>10</v>
-      </c>
       <c r="J162" t="s">
         <v>8</v>
       </c>
@@ -4876,16 +4882,19 @@
       <c r="J163" t="s">
         <v>77</v>
       </c>
+      <c r="K163" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
-        <v>69</v>
+      <c r="A164" t="s">
+        <v>67</v>
       </c>
       <c r="B164" s="6">
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D164" s="17">
         <v>46290</v>
@@ -4897,27 +4906,24 @@
         <v>1</v>
       </c>
       <c r="G164" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H164" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="I164" t="s">
-        <v>10</v>
-      </c>
-      <c r="J164" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A165" s="1" t="s">
-        <v>69</v>
+      <c r="A165" t="s">
+        <v>67</v>
       </c>
       <c r="B165" s="6">
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" s="17">
         <v>46291</v>
@@ -4929,15 +4935,12 @@
         <v>1</v>
       </c>
       <c r="G165" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H165" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="I165" t="s">
-        <v>10</v>
-      </c>
-      <c r="J165" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4961,68 +4964,49 @@
         <v>1</v>
       </c>
       <c r="G166" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H166" t="s">
         <v>61</v>
       </c>
       <c r="I166" t="s">
-        <v>10</v>
-      </c>
-      <c r="J166" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>67</v>
+      </c>
+      <c r="B167" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C167">
+        <v>3</v>
+      </c>
       <c r="D167" s="17">
-        <v>46293</v>
+        <v>46292</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="G167" t="s">
         <v>60</v>
       </c>
       <c r="H167" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="I167" t="s">
-        <v>10</v>
-      </c>
-      <c r="J167" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D168" s="17">
-        <v>46294</v>
-      </c>
-      <c r="G168" t="s">
-        <v>60</v>
-      </c>
-      <c r="H168" t="s">
-        <v>61</v>
-      </c>
-      <c r="I168" t="s">
-        <v>10</v>
-      </c>
-      <c r="J168" t="s">
-        <v>74</v>
-      </c>
+      <c r="D168" s="17"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D169" s="17">
-        <v>46295</v>
-      </c>
-      <c r="G169" t="s">
-        <v>60</v>
-      </c>
-      <c r="H169" t="s">
-        <v>61</v>
-      </c>
-      <c r="I169" t="s">
-        <v>10</v>
-      </c>
-      <c r="J169" t="s">
-        <v>74</v>
-      </c>
+      <c r="D169" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A35DCFB-58DD-4153-83FB-143434DCA358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722666B3-A83A-4640-8229-737CB05689E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="82">
   <si>
     <t>Task</t>
   </si>
@@ -349,6 +349,10 @@
   </si>
   <si>
     <t>Asyraf/Aiman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishnets found at A3B, C3D, D2C. A keychain found at D2C.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4920,7 +4924,7 @@
         <v>67</v>
       </c>
       <c r="B165" s="6">
-        <v>0.14000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="C165">
         <v>3</v>
@@ -4942,6 +4946,9 @@
       </c>
       <c r="I165" t="s">
         <v>75</v>
+      </c>
+      <c r="K165" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
@@ -4978,7 +4985,7 @@
         <v>67</v>
       </c>
       <c r="B167" s="6">
-        <v>0.14000000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="C167">
         <v>3</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722666B3-A83A-4640-8229-737CB05689E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177F9FB1-E45D-42B9-9296-4673FE2AE5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="83">
   <si>
     <t>Task</t>
   </si>
@@ -353,6 +353,10 @@
   </si>
   <si>
     <t>Fishnets found at A3B, C3D, D2C. A keychain found at D2C.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong surface current pushed the AIB into the jacket near Leg C, causing tether entanglement.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -774,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O170"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -4952,14 +4956,14 @@
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
-        <v>69</v>
+      <c r="A166" t="s">
+        <v>67</v>
       </c>
       <c r="B166" s="6">
-        <v>0.22</v>
+        <v>0.45</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" s="17">
         <v>46292</v>
@@ -4971,49 +4975,81 @@
         <v>1</v>
       </c>
       <c r="G166" t="s">
+        <v>80</v>
+      </c>
+      <c r="H166" t="s">
+        <v>79</v>
+      </c>
+      <c r="I166" t="s">
+        <v>77</v>
+      </c>
+      <c r="K166" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B167" s="6">
+        <v>0.44</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" s="17">
+        <v>46293</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G167" t="s">
         <v>10</v>
       </c>
-      <c r="H166" t="s">
+      <c r="H167" t="s">
         <v>61</v>
       </c>
-      <c r="I166" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+      <c r="I167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
         <v>67</v>
       </c>
-      <c r="B167" s="6">
-        <v>0.31</v>
-      </c>
-      <c r="C167">
+      <c r="B168" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C168">
         <v>3</v>
       </c>
-      <c r="D167" s="17">
-        <v>46292</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G167" t="s">
+      <c r="D168" s="17">
+        <v>46293</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G168" t="s">
         <v>60</v>
       </c>
-      <c r="H167" t="s">
+      <c r="H168" t="s">
         <v>78</v>
       </c>
-      <c r="I167" t="s">
+      <c r="I168" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D168" s="17"/>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D169" s="17"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D170" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177F9FB1-E45D-42B9-9296-4673FE2AE5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A148BC5-CB19-4FAC-916D-CC2D1409887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="83">
   <si>
     <t>Task</t>
   </si>
@@ -5046,10 +5046,62 @@
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D169" s="17"/>
+      <c r="A169" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B169" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169" s="17">
+        <v>46294</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G169" t="s">
+        <v>10</v>
+      </c>
+      <c r="H169" t="s">
+        <v>61</v>
+      </c>
+      <c r="I169" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D170" s="17"/>
+      <c r="A170" t="s">
+        <v>67</v>
+      </c>
+      <c r="B170" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C170">
+        <v>3</v>
+      </c>
+      <c r="D170" s="17">
+        <v>46294</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G170" t="s">
+        <v>60</v>
+      </c>
+      <c r="H170" t="s">
+        <v>78</v>
+      </c>
+      <c r="I170" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A148BC5-CB19-4FAC-916D-CC2D1409887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928A79BC-EA48-4829-87FD-9F5FEB19C07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="83">
   <si>
     <t>Task</t>
   </si>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O170"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5050,7 +5050,7 @@
         <v>69</v>
       </c>
       <c r="B169" s="4">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5079,7 +5079,7 @@
         <v>67</v>
       </c>
       <c r="B170" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.76</v>
       </c>
       <c r="C170">
         <v>3</v>
@@ -5101,6 +5101,35 @@
       </c>
       <c r="I170" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B171" s="4">
+        <v>1</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171" s="17">
+        <v>46295</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G171" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" t="s">
+        <v>61</v>
+      </c>
+      <c r="I171" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928A79BC-EA48-4829-87FD-9F5FEB19C07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74BF993-8665-44B1-8A47-4568A3D3C422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="84">
   <si>
     <t>Task</t>
   </si>
@@ -358,6 +358,9 @@
   <si>
     <t>Strong surface current pushed the AIB into the jacket near Leg C, causing tether entanglement.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishing net entangled with thrusters 2, 4, and 6 (resolved).</t>
   </si>
 </sst>
 </file>
@@ -778,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O172"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5132,6 +5135,38 @@
         <v>8</v>
       </c>
     </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>67</v>
+      </c>
+      <c r="B172" s="4">
+        <v>1</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
+      </c>
+      <c r="D172" s="17">
+        <v>46296</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G172" t="s">
+        <v>60</v>
+      </c>
+      <c r="H172" t="s">
+        <v>78</v>
+      </c>
+      <c r="I172" t="s">
+        <v>8</v>
+      </c>
+      <c r="K172" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74BF993-8665-44B1-8A47-4568A3D3C422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C442190C-2918-4211-B3A1-EB003D0B72C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="87">
   <si>
     <t>Task</t>
   </si>
@@ -361,6 +361,18 @@
   </si>
   <si>
     <t>Fishing net entangled with thrusters 2, 4, and 6 (resolved).</t>
+  </si>
+  <si>
+    <t>D12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High current. CTV unable to push on.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -781,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O172"/>
+  <dimension ref="A1:O174"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5167,6 +5179,70 @@
         <v>83</v>
       </c>
     </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B173" s="4">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" s="17">
+        <v>46297</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G173" t="s">
+        <v>60</v>
+      </c>
+      <c r="H173" t="s">
+        <v>78</v>
+      </c>
+      <c r="I173" t="s">
+        <v>77</v>
+      </c>
+      <c r="K173" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>85</v>
+      </c>
+      <c r="B174" s="4">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>2</v>
+      </c>
+      <c r="D174" s="17">
+        <v>46297</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G174" t="s">
+        <v>10</v>
+      </c>
+      <c r="H174" t="s">
+        <v>61</v>
+      </c>
+      <c r="I174" t="s">
+        <v>8</v>
+      </c>
+      <c r="K174" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C442190C-2918-4211-B3A1-EB003D0B72C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A66C66C-EBB0-4D66-80B2-FFE324B934FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="87">
   <si>
     <t>Task</t>
   </si>
@@ -793,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O174"/>
+  <dimension ref="A1:O178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5243,6 +5243,134 @@
         <v>86</v>
       </c>
     </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A175" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B175" s="4">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" s="17">
+        <v>46298</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175" t="s">
+        <v>60</v>
+      </c>
+      <c r="H175" t="s">
+        <v>78</v>
+      </c>
+      <c r="I175" t="s">
+        <v>77</v>
+      </c>
+      <c r="K175" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>85</v>
+      </c>
+      <c r="B176" s="4">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>2</v>
+      </c>
+      <c r="D176" s="17">
+        <v>46298</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G176" t="s">
+        <v>10</v>
+      </c>
+      <c r="H176" t="s">
+        <v>61</v>
+      </c>
+      <c r="I176" t="s">
+        <v>8</v>
+      </c>
+      <c r="K176" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B177" s="4">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177" s="17">
+        <v>46299</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G177" t="s">
+        <v>60</v>
+      </c>
+      <c r="H177" t="s">
+        <v>78</v>
+      </c>
+      <c r="I177" t="s">
+        <v>77</v>
+      </c>
+      <c r="K177" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>85</v>
+      </c>
+      <c r="B178" s="4">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>2</v>
+      </c>
+      <c r="D178" s="17">
+        <v>46299</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G178" t="s">
+        <v>10</v>
+      </c>
+      <c r="H178" t="s">
+        <v>61</v>
+      </c>
+      <c r="I178" t="s">
+        <v>8</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A66C66C-EBB0-4D66-80B2-FFE324B934FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A08F1-79F9-4EDE-BBA6-1CDECC2BA8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="87">
   <si>
     <t>Task</t>
   </si>
@@ -5245,13 +5245,10 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="B175" s="4">
         <v>0</v>
-      </c>
-      <c r="C175">
-        <v>1</v>
       </c>
       <c r="D175" s="17">
         <v>46298</v>
@@ -5263,30 +5260,27 @@
         <v>45</v>
       </c>
       <c r="G175" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H175" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I175" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K175" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>85</v>
+      <c r="A176" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="B176" s="4">
         <v>0</v>
       </c>
-      <c r="C176">
-        <v>2</v>
-      </c>
       <c r="D176" s="17">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>42</v>
@@ -5295,81 +5289,30 @@
         <v>45</v>
       </c>
       <c r="G176" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="H176" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="I176" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="K176" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A177" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B177" s="4">
-        <v>0</v>
-      </c>
-      <c r="C177">
-        <v>1</v>
-      </c>
-      <c r="D177" s="17">
-        <v>46299</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G177" t="s">
-        <v>60</v>
-      </c>
-      <c r="H177" t="s">
-        <v>78</v>
-      </c>
-      <c r="I177" t="s">
-        <v>77</v>
-      </c>
-      <c r="K177" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="A177" s="1"/>
+      <c r="D177" s="17"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="1"/>
+      <c r="K177" s="1"/>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>85</v>
-      </c>
-      <c r="B178" s="4">
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <v>2</v>
-      </c>
-      <c r="D178" s="17">
-        <v>46299</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G178" t="s">
-        <v>10</v>
-      </c>
-      <c r="H178" t="s">
-        <v>61</v>
-      </c>
-      <c r="I178" t="s">
-        <v>8</v>
-      </c>
-      <c r="K178" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="D178" s="17"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="1"/>
+      <c r="K178" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077A08F1-79F9-4EDE-BBA6-1CDECC2BA8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B2E612-784C-4B04-A6F2-417CD08089D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="87">
   <si>
     <t>Task</t>
   </si>
@@ -5302,17 +5302,62 @@
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A177" s="1"/>
-      <c r="D177" s="17"/>
-      <c r="E177" s="2"/>
-      <c r="F177" s="1"/>
-      <c r="K177" s="1"/>
+      <c r="A177" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B177" s="4">
+        <v>0</v>
+      </c>
+      <c r="D177" s="17">
+        <v>46300</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G177" t="s">
+        <v>80</v>
+      </c>
+      <c r="H177" t="s">
+        <v>79</v>
+      </c>
+      <c r="I177" t="s">
+        <v>74</v>
+      </c>
+      <c r="K177" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D178" s="17"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="1"/>
-      <c r="K178" s="1"/>
+      <c r="A178" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B178" s="4">
+        <v>0</v>
+      </c>
+      <c r="D178" s="17">
+        <v>46301</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G178" t="s">
+        <v>80</v>
+      </c>
+      <c r="H178" t="s">
+        <v>79</v>
+      </c>
+      <c r="I178" t="s">
+        <v>74</v>
+      </c>
+      <c r="K178" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B2E612-784C-4B04-A6F2-417CD08089D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC8CA41-E3B7-4F0F-B185-42081F1F8D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="88">
   <si>
     <t>Task</t>
   </si>
@@ -373,6 +373,9 @@
   <si>
     <t>High current. CTV unable to push on.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onshore</t>
   </si>
 </sst>
 </file>
@@ -793,13 +796,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O178"/>
+  <dimension ref="A1:O188"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.59765625" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.59765625" customWidth="1"/>
     <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
@@ -5359,6 +5362,162 @@
         <v>15</v>
       </c>
     </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B179" s="4">
+        <v>0</v>
+      </c>
+      <c r="D179" s="17">
+        <v>46302</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G179" t="s">
+        <v>80</v>
+      </c>
+      <c r="H179" t="s">
+        <v>79</v>
+      </c>
+      <c r="I179" t="s">
+        <v>74</v>
+      </c>
+      <c r="K179" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B180" s="4">
+        <v>0</v>
+      </c>
+      <c r="D180" s="17">
+        <v>46303</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I180" t="s">
+        <v>74</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B181" s="4">
+        <v>0</v>
+      </c>
+      <c r="D181" s="17">
+        <v>46304</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I181" t="s">
+        <v>74</v>
+      </c>
+      <c r="K181" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B182" s="4">
+        <v>0</v>
+      </c>
+      <c r="D182" s="17">
+        <v>46305</v>
+      </c>
+      <c r="E182" t="s">
+        <v>87</v>
+      </c>
+      <c r="F182" t="s">
+        <v>4</v>
+      </c>
+      <c r="I182" t="s">
+        <v>74</v>
+      </c>
+      <c r="K182" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B183" s="4">
+        <v>0</v>
+      </c>
+      <c r="D183" s="17">
+        <v>46306</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I183" t="s">
+        <v>74</v>
+      </c>
+      <c r="K183" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B184" s="4">
+        <v>0</v>
+      </c>
+      <c r="D184" s="17">
+        <v>46307</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I184" t="s">
+        <v>74</v>
+      </c>
+      <c r="K184" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="2"/>
+      <c r="F188" s="1"/>
+      <c r="G188" s="1"/>
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+      <c r="J188" s="1"/>
+      <c r="K188" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC8CA41-E3B7-4F0F-B185-42081F1F8D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB53E3-F43A-4E1A-83DD-5384DC114D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="91">
   <si>
     <t>Task</t>
   </si>
@@ -376,6 +376,17 @@
   </si>
   <si>
     <t>onshore</t>
+  </si>
+  <si>
+    <t>Shafiq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continued last year's MGM inspection at D08 Leg A</t>
+  </si>
+  <si>
+    <t>Continued last year's MGM inspection at D12 Leg A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5506,6 +5517,67 @@
         <v>18</v>
       </c>
     </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B185" s="4">
+        <v>1</v>
+      </c>
+      <c r="D185" s="17">
+        <v>46308</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G185" t="s">
+        <v>10</v>
+      </c>
+      <c r="H185" t="s">
+        <v>61</v>
+      </c>
+      <c r="I185" t="s">
+        <v>8</v>
+      </c>
+      <c r="K185" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>85</v>
+      </c>
+      <c r="B186" s="4">
+        <v>1</v>
+      </c>
+      <c r="D186" s="17">
+        <v>46308</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G186" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>88</v>
+      </c>
+      <c r="I186" t="s">
+        <v>78</v>
+      </c>
+      <c r="J186" t="s">
+        <v>77</v>
+      </c>
+      <c r="K186" t="s">
+        <v>89</v>
+      </c>
+    </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="C188" s="1"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB53E3-F43A-4E1A-83DD-5384DC114D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44293120-4C7D-4C95-99CA-E9574101A1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5524,6 +5524,9 @@
       <c r="B185" s="4">
         <v>1</v>
       </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
       <c r="D185" s="17">
         <v>46308</v>
       </c>
@@ -5552,6 +5555,9 @@
       </c>
       <c r="B186" s="4">
         <v>1</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
       </c>
       <c r="D186" s="17">
         <v>46308</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44293120-4C7D-4C95-99CA-E9574101A1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61B06B-FD37-486C-9F44-E6BEB26CEC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="93">
   <si>
     <t>Task</t>
   </si>
@@ -386,6 +386,14 @@
   </si>
   <si>
     <t>Continued last year's MGM inspection at D12 Leg A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fremmy/Zaidi/Shafiq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dil/Aiman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5584,17 +5592,63 @@
         <v>89</v>
       </c>
     </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B187" s="4">
+        <v>0</v>
+      </c>
+      <c r="D187" s="17">
+        <v>46309</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G187" t="s">
+        <v>92</v>
+      </c>
+      <c r="H187" t="s">
+        <v>91</v>
+      </c>
+      <c r="I187" t="s">
+        <v>74</v>
+      </c>
+      <c r="K187" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
-      <c r="H188" s="1"/>
-      <c r="I188" s="1"/>
-      <c r="J188" s="1"/>
-      <c r="K188" s="1"/>
+      <c r="A188" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B188" s="4">
+        <v>0</v>
+      </c>
+      <c r="D188" s="17">
+        <v>46310</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G188" t="s">
+        <v>92</v>
+      </c>
+      <c r="H188" t="s">
+        <v>91</v>
+      </c>
+      <c r="I188" t="s">
+        <v>74</v>
+      </c>
+      <c r="K188" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E61B06B-FD37-486C-9F44-E6BEB26CEC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66EAD9E-99FB-4FD6-8B01-41ADC3BD2EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="97">
   <si>
     <t>Task</t>
   </si>
@@ -394,6 +394,22 @@
   </si>
   <si>
     <t>Dil/Aiman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continuation of last year's work</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continuation of last year's work / Unable to commence operations due to crane issue.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -815,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O190"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5650,6 +5666,70 @@
         <v>15</v>
       </c>
     </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B189" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+      <c r="D189" s="17">
+        <v>46311</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G189" t="s">
+        <v>7</v>
+      </c>
+      <c r="H189" t="s">
+        <v>10</v>
+      </c>
+      <c r="I189" t="s">
+        <v>61</v>
+      </c>
+      <c r="J189" t="s">
+        <v>8</v>
+      </c>
+      <c r="K189" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A190" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C190">
+        <v>4</v>
+      </c>
+      <c r="D190" s="17">
+        <v>46311</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G190" t="s">
+        <v>88</v>
+      </c>
+      <c r="H190" t="s">
+        <v>78</v>
+      </c>
+      <c r="I190" t="s">
+        <v>77</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66EAD9E-99FB-4FD6-8B01-41ADC3BD2EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F4B539-E5D8-48CF-8CFE-D21674B5F3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5705,6 +5705,9 @@
       <c r="A190" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="B190" s="4">
+        <v>1</v>
+      </c>
       <c r="C190">
         <v>4</v>
       </c>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F4B539-E5D8-48CF-8CFE-D21674B5F3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004864D-D642-439E-9D54-2CCF71639FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="101">
   <si>
     <t>Task</t>
   </si>
@@ -410,6 +410,23 @@
   </si>
   <si>
     <t>Continuation of last year's work / Unable to commence operations due to crane issue.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Strong currents – Waiting on Weather.
+2.No power supply at TP – Move to another jacket tomorrow.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unable to climb the tower due to an SRL issue. Switched to D01.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -831,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O190"/>
+  <dimension ref="A1:O193"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5733,6 +5750,99 @@
         <v>95</v>
       </c>
     </row>
+    <row r="191" spans="1:11" ht="29" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B191" s="4">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+      <c r="D191" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G191" t="s">
+        <v>10</v>
+      </c>
+      <c r="H191" t="s">
+        <v>61</v>
+      </c>
+      <c r="I191" t="s">
+        <v>8</v>
+      </c>
+      <c r="K191" s="18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A192" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B192" s="4">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>2</v>
+      </c>
+      <c r="D192" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G192" t="s">
+        <v>88</v>
+      </c>
+      <c r="H192" t="s">
+        <v>78</v>
+      </c>
+      <c r="I192" t="s">
+        <v>77</v>
+      </c>
+      <c r="K192" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A193" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B193" s="4">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="D193" s="17">
+        <v>46312</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G193" t="s">
+        <v>88</v>
+      </c>
+      <c r="H193" t="s">
+        <v>78</v>
+      </c>
+      <c r="I193" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D004864D-D642-439E-9D54-2CCF71639FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048EDFFE-93AA-4796-982F-2958C7AD1C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="104">
   <si>
     <t>Task</t>
   </si>
@@ -427,6 +427,18 @@
   </si>
   <si>
     <t>D01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong currents – Waiting on Weather.</t>
+  </si>
+  <si>
+    <t>1.Assisted Siemens technicians with SRL replacement during work at height.
+2. Strong currents – Waiting on Weather.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +528,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -565,6 +577,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -848,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O197"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5814,7 +5832,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>100</v>
       </c>
@@ -5842,6 +5860,73 @@
       <c r="I193" t="s">
         <v>77</v>
       </c>
+      <c r="K193" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A194" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+      <c r="D194" s="17">
+        <v>46313</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G194" t="s">
+        <v>88</v>
+      </c>
+      <c r="H194" t="s">
+        <v>78</v>
+      </c>
+      <c r="I194" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" ht="29" x14ac:dyDescent="0.3">
+      <c r="A195" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B195" s="4">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" s="17">
+        <v>46313</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G195" t="s">
+        <v>10</v>
+      </c>
+      <c r="H195" t="s">
+        <v>61</v>
+      </c>
+      <c r="I195" t="s">
+        <v>8</v>
+      </c>
+      <c r="K195" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K196" s="19"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K197" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048EDFFE-93AA-4796-982F-2958C7AD1C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355E613E-9A25-4AE8-B2E9-B3F8322CEF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="105">
   <si>
     <t>Task</t>
   </si>
@@ -439,6 +439,10 @@
   <si>
     <t>1.Assisted Siemens technicians with SRL replacement during work at height.
 2. Strong currents – Waiting on Weather.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to be confirmed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -528,7 +532,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -577,9 +581,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -866,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O197"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5868,6 +5869,9 @@
       <c r="A194" s="1" t="s">
         <v>100</v>
       </c>
+      <c r="B194" s="4">
+        <v>0</v>
+      </c>
       <c r="C194">
         <v>2</v>
       </c>
@@ -5888,6 +5892,9 @@
       </c>
       <c r="I194" t="s">
         <v>77</v>
+      </c>
+      <c r="K194" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="195" spans="1:11" ht="29" x14ac:dyDescent="0.3">
@@ -5918,15 +5925,217 @@
       <c r="I195" t="s">
         <v>8</v>
       </c>
-      <c r="K195" s="20" t="s">
+      <c r="K195" s="19" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K196" s="19"/>
+      <c r="A196" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B196" s="4">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+      <c r="D196" s="17">
+        <v>46314</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F196" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G196" t="s">
+        <v>88</v>
+      </c>
+      <c r="H196" t="s">
+        <v>78</v>
+      </c>
+      <c r="I196" t="s">
+        <v>77</v>
+      </c>
+      <c r="K196" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K197" s="19"/>
+      <c r="A197" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B197" s="4">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+      <c r="D197" s="17">
+        <v>46314</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G197" t="s">
+        <v>64</v>
+      </c>
+      <c r="H197" t="s">
+        <v>10</v>
+      </c>
+      <c r="I197" t="s">
+        <v>61</v>
+      </c>
+      <c r="J197" t="s">
+        <v>8</v>
+      </c>
+      <c r="K197" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B198" s="4">
+        <v>0</v>
+      </c>
+      <c r="D198" s="17">
+        <v>46315</v>
+      </c>
+      <c r="E198" s="2"/>
+      <c r="F198" s="1"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A199" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B199" s="4">
+        <v>0</v>
+      </c>
+      <c r="D199" s="17">
+        <v>46316</v>
+      </c>
+      <c r="E199" s="2"/>
+      <c r="F199" s="1"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A200" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B200" s="4">
+        <v>0</v>
+      </c>
+      <c r="D200" s="17">
+        <v>46317</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I200" t="s">
+        <v>74</v>
+      </c>
+      <c r="K200" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A201" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B201" s="4">
+        <v>0</v>
+      </c>
+      <c r="D201" s="17">
+        <v>46318</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I201" t="s">
+        <v>74</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B202" s="4">
+        <v>0</v>
+      </c>
+      <c r="D202" s="17">
+        <v>46319</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I202" t="s">
+        <v>74</v>
+      </c>
+      <c r="K202" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A203" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B203" s="4">
+        <v>0</v>
+      </c>
+      <c r="D203" s="17">
+        <v>46320</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I203" t="s">
+        <v>74</v>
+      </c>
+      <c r="K203" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A204" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B204" s="4">
+        <v>0</v>
+      </c>
+      <c r="D204" s="17">
+        <v>46321</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I204" t="s">
+        <v>74</v>
+      </c>
+      <c r="K204" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355E613E-9A25-4AE8-B2E9-B3F8322CEF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167FC59E-8F79-4A0E-8AEC-1A1DAF017FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="C152" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="15">
         <v>46278</v>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" s="17">
         <v>46282</v>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167FC59E-8F79-4A0E-8AEC-1A1DAF017FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28F506E-3DA0-4B2A-9F0B-B48FCD44E422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="105">
   <si>
     <t>Task</t>
   </si>
@@ -867,7 +867,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O204"/>
+  <dimension ref="A1:O205"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.09765625" bestFit="1" customWidth="1"/>
@@ -5998,52 +5998,77 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B198" s="4">
         <v>0</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
       </c>
       <c r="D198" s="17">
         <v>46315</v>
       </c>
-      <c r="E198" s="2"/>
-      <c r="F198" s="1"/>
+      <c r="E198" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G198" t="s">
+        <v>88</v>
+      </c>
+      <c r="H198" t="s">
+        <v>78</v>
+      </c>
+      <c r="I198" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B199" s="4">
         <v>0</v>
       </c>
+      <c r="C199">
+        <v>2</v>
+      </c>
       <c r="D199" s="17">
-        <v>46316</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" s="1"/>
+        <v>46315</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G199" t="s">
+        <v>64</v>
+      </c>
+      <c r="H199" t="s">
+        <v>10</v>
+      </c>
+      <c r="I199" t="s">
+        <v>61</v>
+      </c>
+      <c r="J199" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="B200" s="4">
         <v>0</v>
       </c>
       <c r="D200" s="17">
-        <v>46317</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I200" t="s">
-        <v>74</v>
-      </c>
-      <c r="K200" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>46316</v>
+      </c>
+      <c r="E200" s="2"/>
+      <c r="F200" s="1"/>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
@@ -6053,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="D201" s="17">
-        <v>46318</v>
+        <v>46317</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>42</v>
@@ -6076,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="D202" s="17">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>42</v>
@@ -6099,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="D203" s="17">
-        <v>46320</v>
+        <v>46319</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>42</v>
@@ -6122,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="D204" s="17">
-        <v>46321</v>
+        <v>46320</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>42</v>
@@ -6134,6 +6159,29 @@
         <v>74</v>
       </c>
       <c r="K204" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A205" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B205" s="4">
+        <v>0</v>
+      </c>
+      <c r="D205" s="17">
+        <v>46321</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F205" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I205" t="s">
+        <v>74</v>
+      </c>
+      <c r="K205" s="1" t="s">
         <v>18</v>
       </c>
     </row>

--- a/progress.xlsx
+++ b/progress.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ali.chang\Desktop\Ali正力\專案\S2603BEX50\offshore gantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28F506E-3DA0-4B2A-9F0B-B48FCD44E422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BE7428-DD91-4C4C-93F7-0E7CEB02598D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="106">
   <si>
     <t>Task</t>
   </si>
@@ -442,7 +442,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>to be confirmed</t>
+    <t>Shafiq/Aiman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WoW – Typhoon Champi approaching Taiwan.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5981,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H197" t="s">
         <v>10</v>
@@ -6024,6 +6028,9 @@
       <c r="I198" t="s">
         <v>77</v>
       </c>
+      <c r="K198" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
@@ -6051,15 +6058,15 @@
         <v>10</v>
       </c>
       <c r="I199" t="s">
-        <v>61</v>
-      </c>
-      <c r="J199" t="s">
         <v>8</v>
+      </c>
+      <c r="K199" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="B200" s="4">
         <v>0</v>
@@ -6067,8 +6074,24 @@
       <c r="D200" s="17">
         <v>46316</v>
       </c>
-      <c r="E200" s="2"/>
-      <c r="F200" s="1"/>
+      <c r="E200" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G200" t="s">
+        <v>104</v>
+      </c>
+      <c r="H200" t="s">
+        <v>91</v>
+      </c>
+      <c r="I200" t="s">
+        <v>74</v>
+      </c>
+      <c r="K200" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
